--- a/artfynd/A 50952-2024 artfynd.xlsx
+++ b/artfynd/A 50952-2024 artfynd.xlsx
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126393407</v>
+        <v>126393440</v>
       </c>
       <c r="B7" t="n">
-        <v>91238</v>
+        <v>75077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587565</v>
+        <v>588320</v>
       </c>
       <c r="R7" t="n">
-        <v>7261001</v>
+        <v>7260748</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126393440</v>
+        <v>126393407</v>
       </c>
       <c r="B8" t="n">
-        <v>75077</v>
+        <v>91238</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588320</v>
+        <v>587565</v>
       </c>
       <c r="R8" t="n">
-        <v>7260748</v>
+        <v>7261001</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 50952-2024 artfynd.xlsx
+++ b/artfynd/A 50952-2024 artfynd.xlsx
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126393440</v>
+        <v>126393407</v>
       </c>
       <c r="B7" t="n">
-        <v>75077</v>
+        <v>91238</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588320</v>
+        <v>587565</v>
       </c>
       <c r="R7" t="n">
-        <v>7260748</v>
+        <v>7261001</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126393407</v>
+        <v>126393440</v>
       </c>
       <c r="B8" t="n">
-        <v>91238</v>
+        <v>75077</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587565</v>
+        <v>588320</v>
       </c>
       <c r="R8" t="n">
-        <v>7261001</v>
+        <v>7260748</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 50952-2024 artfynd.xlsx
+++ b/artfynd/A 50952-2024 artfynd.xlsx
@@ -1841,37 +1841,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126393406</v>
+        <v>126393499</v>
       </c>
       <c r="B13" t="n">
-        <v>91242</v>
+        <v>98352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1879,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587565</v>
+        <v>588527</v>
       </c>
       <c r="R13" t="n">
-        <v>7261001</v>
+        <v>7260719</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,38 +1948,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126393499</v>
+        <v>126393406</v>
       </c>
       <c r="B14" t="n">
-        <v>98352</v>
+        <v>91242</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588527</v>
+        <v>587565</v>
       </c>
       <c r="R14" t="n">
-        <v>7260719</v>
+        <v>7261001</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 50952-2024 artfynd.xlsx
+++ b/artfynd/A 50952-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126393380</v>
       </c>
       <c r="B2" t="n">
-        <v>91611</v>
+        <v>91614</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126393397</v>
       </c>
       <c r="B3" t="n">
-        <v>82789</v>
+        <v>82792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126393392</v>
       </c>
       <c r="B4" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>126393359</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>126393430</v>
       </c>
       <c r="B6" t="n">
-        <v>56839</v>
+        <v>56840</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>126393407</v>
       </c>
       <c r="B7" t="n">
-        <v>91238</v>
+        <v>91241</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>126393440</v>
       </c>
       <c r="B8" t="n">
-        <v>75077</v>
+        <v>75080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>126393402</v>
       </c>
       <c r="B9" t="n">
-        <v>79056</v>
+        <v>79059</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126393348</v>
+        <v>126393393</v>
       </c>
       <c r="B10" t="n">
-        <v>77941</v>
+        <v>79059</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1534,21 +1534,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>314</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586736</v>
+        <v>586963</v>
       </c>
       <c r="R10" t="n">
-        <v>7261329</v>
+        <v>7261440</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126393414</v>
+        <v>126393348</v>
       </c>
       <c r="B11" t="n">
-        <v>75064</v>
+        <v>77944</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1640,21 +1640,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587925</v>
+        <v>586736</v>
       </c>
       <c r="R11" t="n">
-        <v>7260892</v>
+        <v>7261329</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126393393</v>
+        <v>126393414</v>
       </c>
       <c r="B12" t="n">
-        <v>79056</v>
+        <v>75067</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>864</v>
+        <v>308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586963</v>
+        <v>587925</v>
       </c>
       <c r="R12" t="n">
-        <v>7261440</v>
+        <v>7260892</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,38 +1841,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126393499</v>
+        <v>126393406</v>
       </c>
       <c r="B13" t="n">
-        <v>98352</v>
+        <v>91245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1880,10 +1879,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588527</v>
+        <v>587565</v>
       </c>
       <c r="R13" t="n">
-        <v>7260719</v>
+        <v>7261001</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,37 +1947,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126393406</v>
+        <v>126393499</v>
       </c>
       <c r="B14" t="n">
-        <v>91242</v>
+        <v>98361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587565</v>
+        <v>588527</v>
       </c>
       <c r="R14" t="n">
-        <v>7261001</v>
+        <v>7260719</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,7 +2057,7 @@
         <v>126393436</v>
       </c>
       <c r="B15" t="n">
-        <v>91256</v>
+        <v>91259</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>126393426</v>
       </c>
       <c r="B16" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>126393358</v>
       </c>
       <c r="B17" t="n">
-        <v>75072</v>
+        <v>75075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>126393518</v>
       </c>
       <c r="B18" t="n">
-        <v>78383</v>
+        <v>78386</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>126393423</v>
       </c>
       <c r="B19" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>126393371</v>
       </c>
       <c r="B20" t="n">
-        <v>91238</v>
+        <v>91241</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>126393505</v>
       </c>
       <c r="B21" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>126393530</v>
       </c>
       <c r="B22" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>126393506</v>
       </c>
       <c r="B23" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 50952-2024 artfynd.xlsx
+++ b/artfynd/A 50952-2024 artfynd.xlsx
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126393393</v>
+        <v>126393348</v>
       </c>
       <c r="B10" t="n">
-        <v>79059</v>
+        <v>77944</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1534,21 +1534,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>864</v>
+        <v>314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586963</v>
+        <v>586736</v>
       </c>
       <c r="R10" t="n">
-        <v>7261440</v>
+        <v>7261329</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126393348</v>
+        <v>126393414</v>
       </c>
       <c r="B11" t="n">
-        <v>77944</v>
+        <v>75067</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1640,21 +1640,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586736</v>
+        <v>587925</v>
       </c>
       <c r="R11" t="n">
-        <v>7261329</v>
+        <v>7260892</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126393414</v>
+        <v>126393393</v>
       </c>
       <c r="B12" t="n">
-        <v>75067</v>
+        <v>79059</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>308</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587925</v>
+        <v>586963</v>
       </c>
       <c r="R12" t="n">
-        <v>7260892</v>
+        <v>7261440</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2054,10 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126393436</v>
+        <v>126393426</v>
       </c>
       <c r="B15" t="n">
-        <v>91259</v>
+        <v>91245</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,21 +2065,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>588317</v>
+        <v>587966</v>
       </c>
       <c r="R15" t="n">
-        <v>7260775</v>
+        <v>7261076</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2160,10 +2160,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126393426</v>
+        <v>126393436</v>
       </c>
       <c r="B16" t="n">
-        <v>91245</v>
+        <v>91259</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2171,21 +2171,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587966</v>
+        <v>588317</v>
       </c>
       <c r="R16" t="n">
-        <v>7261076</v>
+        <v>7260775</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2690,32 +2690,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126393505</v>
+        <v>126393530</v>
       </c>
       <c r="B21" t="n">
-        <v>91699</v>
+        <v>91245</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588749</v>
+        <v>588966</v>
       </c>
       <c r="R21" t="n">
-        <v>7260477</v>
+        <v>7260416</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2796,32 +2796,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126393530</v>
+        <v>126393505</v>
       </c>
       <c r="B22" t="n">
-        <v>91245</v>
+        <v>91699</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2834,10 +2834,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588966</v>
+        <v>588749</v>
       </c>
       <c r="R22" t="n">
-        <v>7260416</v>
+        <v>7260477</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 50952-2024 artfynd.xlsx
+++ b/artfynd/A 50952-2024 artfynd.xlsx
@@ -1841,37 +1841,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126393406</v>
+        <v>126393499</v>
       </c>
       <c r="B13" t="n">
-        <v>91245</v>
+        <v>98361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1879,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587565</v>
+        <v>588527</v>
       </c>
       <c r="R13" t="n">
-        <v>7261001</v>
+        <v>7260719</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,38 +1948,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126393499</v>
+        <v>126393406</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>91245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>588527</v>
+        <v>587565</v>
       </c>
       <c r="R14" t="n">
-        <v>7260719</v>
+        <v>7261001</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 50952-2024 artfynd.xlsx
+++ b/artfynd/A 50952-2024 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126393359</v>
+        <v>126393430</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>56840</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,26 +1004,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1031,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586764</v>
+        <v>588272</v>
       </c>
       <c r="R5" t="n">
-        <v>7261337</v>
+        <v>7260876</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,7 +1076,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126393430</v>
+        <v>126393359</v>
       </c>
       <c r="B6" t="n">
-        <v>56840</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,27 +1110,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1138,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588272</v>
+        <v>586764</v>
       </c>
       <c r="R6" t="n">
-        <v>7260876</v>
+        <v>7261337</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,6 +1181,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1841,38 +1841,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126393499</v>
+        <v>126393406</v>
       </c>
       <c r="B13" t="n">
-        <v>98361</v>
+        <v>91245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1880,10 +1879,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588527</v>
+        <v>587565</v>
       </c>
       <c r="R13" t="n">
-        <v>7260719</v>
+        <v>7261001</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,37 +1947,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126393406</v>
+        <v>126393499</v>
       </c>
       <c r="B14" t="n">
-        <v>91245</v>
+        <v>98361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587565</v>
+        <v>588527</v>
       </c>
       <c r="R14" t="n">
-        <v>7261001</v>
+        <v>7260719</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 50952-2024 artfynd.xlsx
+++ b/artfynd/A 50952-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126393380</v>
+        <v>126393348</v>
       </c>
       <c r="B2" t="n">
-        <v>91614</v>
+        <v>78350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1506</v>
+        <v>314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586887</v>
+        <v>586736</v>
       </c>
       <c r="R2" t="n">
-        <v>7261396</v>
+        <v>7261329</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126393397</v>
+        <v>126393371</v>
       </c>
       <c r="B3" t="n">
-        <v>82792</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587299</v>
+        <v>586816</v>
       </c>
       <c r="R3" t="n">
-        <v>7261151</v>
+        <v>7261366</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126393392</v>
+        <v>126393359</v>
       </c>
       <c r="B4" t="n">
-        <v>91263</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586963</v>
+        <v>586764</v>
       </c>
       <c r="R4" t="n">
-        <v>7261440</v>
+        <v>7261337</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126393359</v>
+        <v>126393358</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>83307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126393430</v>
+        <v>126393414</v>
       </c>
       <c r="B6" t="n">
-        <v>56840</v>
+        <v>83299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,27 +1110,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1138,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588272</v>
+        <v>587925</v>
       </c>
       <c r="R6" t="n">
-        <v>7260876</v>
+        <v>7260892</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,6 +1181,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126393407</v>
+        <v>126393423</v>
       </c>
       <c r="B7" t="n">
-        <v>91241</v>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587565</v>
+        <v>587966</v>
       </c>
       <c r="R7" t="n">
-        <v>7261001</v>
+        <v>7261076</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126393440</v>
+        <v>126393393</v>
       </c>
       <c r="B8" t="n">
-        <v>75080</v>
+        <v>79406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1467</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588320</v>
+        <v>586963</v>
       </c>
       <c r="R8" t="n">
-        <v>7260748</v>
+        <v>7261440</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,7 +1420,7 @@
         <v>126393402</v>
       </c>
       <c r="B9" t="n">
-        <v>79059</v>
+        <v>79406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126393348</v>
+        <v>126393407</v>
       </c>
       <c r="B10" t="n">
-        <v>77944</v>
+        <v>91905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1534,21 +1534,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>314</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586736</v>
+        <v>587565</v>
       </c>
       <c r="R10" t="n">
-        <v>7261329</v>
+        <v>7261001</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126393414</v>
+        <v>126393406</v>
       </c>
       <c r="B11" t="n">
-        <v>75067</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1640,21 +1640,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587925</v>
+        <v>587565</v>
       </c>
       <c r="R11" t="n">
-        <v>7260892</v>
+        <v>7261001</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126393393</v>
+        <v>126393426</v>
       </c>
       <c r="B12" t="n">
-        <v>79059</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586963</v>
+        <v>587966</v>
       </c>
       <c r="R12" t="n">
-        <v>7261440</v>
+        <v>7261076</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,38 +1841,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126393499</v>
+        <v>126393506</v>
       </c>
       <c r="B13" t="n">
-        <v>98361</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1880,10 +1879,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>588527</v>
+        <v>588749</v>
       </c>
       <c r="R13" t="n">
-        <v>7260719</v>
+        <v>7260477</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126393406</v>
+        <v>126393530</v>
       </c>
       <c r="B14" t="n">
-        <v>91245</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,10 +1985,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587565</v>
+        <v>588966</v>
       </c>
       <c r="R14" t="n">
-        <v>7261001</v>
+        <v>7260416</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2054,32 +2053,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126393426</v>
+        <v>126393436</v>
       </c>
       <c r="B15" t="n">
-        <v>91245</v>
+        <v>91923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2092,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>587966</v>
+        <v>588317</v>
       </c>
       <c r="R15" t="n">
-        <v>7261076</v>
+        <v>7260775</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2160,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126393436</v>
+        <v>126393505</v>
       </c>
       <c r="B16" t="n">
-        <v>91259</v>
+        <v>92369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2171,21 +2170,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2197,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>588317</v>
+        <v>588749</v>
       </c>
       <c r="R16" t="n">
-        <v>7260775</v>
+        <v>7260477</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2266,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126393358</v>
+        <v>126393397</v>
       </c>
       <c r="B17" t="n">
-        <v>75075</v>
+        <v>83173</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2277,21 +2276,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2304,10 +2303,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586764</v>
+        <v>587299</v>
       </c>
       <c r="R17" t="n">
-        <v>7261337</v>
+        <v>7261151</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126393518</v>
+        <v>126393440</v>
       </c>
       <c r="B18" t="n">
-        <v>78386</v>
+        <v>83312</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,21 +2382,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6437</v>
+        <v>1467</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2410,10 +2409,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>588843</v>
+        <v>588320</v>
       </c>
       <c r="R18" t="n">
-        <v>7260436</v>
+        <v>7260748</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2478,32 +2477,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126393423</v>
+        <v>126393380</v>
       </c>
       <c r="B19" t="n">
-        <v>91541</v>
+        <v>92292</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1506</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2516,10 +2515,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587966</v>
+        <v>586887</v>
       </c>
       <c r="R19" t="n">
-        <v>7261076</v>
+        <v>7261396</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126393371</v>
+        <v>126393518</v>
       </c>
       <c r="B20" t="n">
-        <v>91241</v>
+        <v>78730</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2595,21 +2594,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2622,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586816</v>
+        <v>588843</v>
       </c>
       <c r="R20" t="n">
-        <v>7261366</v>
+        <v>7260436</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2690,37 +2689,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126393530</v>
+        <v>126393430</v>
       </c>
       <c r="B21" t="n">
-        <v>91245</v>
+        <v>57132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>588966</v>
+        <v>588272</v>
       </c>
       <c r="R21" t="n">
-        <v>7260416</v>
+        <v>7260876</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2772,7 +2772,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2796,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126393505</v>
+        <v>126393499</v>
       </c>
       <c r="B22" t="n">
-        <v>91699</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2807,26 +2806,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2834,10 +2834,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>588749</v>
+        <v>588527</v>
       </c>
       <c r="R22" t="n">
-        <v>7260477</v>
+        <v>7260719</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2899,112 +2899,6 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>126393506</v>
-      </c>
-      <c r="B23" t="n">
-        <v>91245</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Naturskog söder om Åbacka, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>588749</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7260477</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Luckig grannaturskog på frisk/fuktig mark</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50952-2024 artfynd.xlsx
+++ b/artfynd/A 50952-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126393414</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126393348</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126393423</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126393393</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126393402</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126393371</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126393407</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126393406</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126393426</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126393506</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,6 +1893,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126393530</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,6 +2004,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126393436</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2050,6 +2115,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126393505</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2156,6 +2226,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126393397</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2262,6 +2337,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126393440</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2368,6 +2448,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126393380</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2474,6 +2559,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126393359</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2580,6 +2670,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126393518</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2686,6 +2781,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126393358</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2792,6 +2892,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126393430</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2899,8 +3004,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126393499</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>